--- a/preview/pr-14/CodeSystem-dem-antwort.xlsx
+++ b/preview/pr-14/CodeSystem-dem-antwort.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:08:36+00:00</t>
+    <t>2026-09-30T09:23:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-14/CodeSystem-dem-antwort.xlsx
+++ b/preview/pr-14/CodeSystem-dem-antwort.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:23:41+00:00</t>
+    <t>2026-09-30T09:31:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-14/CodeSystem-dem-antwort.xlsx
+++ b/preview/pr-14/CodeSystem-dem-antwort.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:31:14+00:00</t>
+    <t>2026-09-30T09:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
